--- a/7rmartsupermarkets/src/test/resources/testdata.xlsx
+++ b/7rmartsupermarkets/src/test/resources/testdata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manji\eclipse-workspace\7rmartsupermarkets\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manji\git\SuperMarket\7rmartsupermarkets\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6D4196-268A-41A0-953C-2166C410C80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C502015B-F40B-4093-8054-D3E23EEA3A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="6000" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="5" xr2:uid="{3B5AFD65-E1B8-435E-8EA0-872F146760E8}"/>
+    <workbookView xWindow="4290" yWindow="4185" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{3B5AFD65-E1B8-435E-8EA0-872F146760E8}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>Password</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>toromnto@gmaio.com</t>
+  </si>
+  <si>
+    <t>sui</t>
   </si>
 </sst>
 </file>
@@ -712,10 +715,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>1</v>
